--- a/diseases/d023/2000-2004.xlsx
+++ b/diseases/d023/2000-2004.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1309,9 +1306,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1853,9 +1847,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -2397,9 +2388,6 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -2941,9 +2929,6 @@
       <c r="O14" t="n">
         <v>1</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.02226741517840542</v>
       </c>
@@ -3485,9 +3470,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -4029,9 +4011,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -4573,9 +4552,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -5117,9 +5093,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -5661,9 +5634,6 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -6205,9 +6175,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
@@ -6749,9 +6716,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -7293,9 +7257,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -7837,9 +7798,6 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
@@ -8233,9 +8191,6 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -8529,9 +8484,6 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
@@ -8825,9 +8777,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -9121,9 +9070,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -9417,9 +9363,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -9713,9 +9656,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -10009,9 +9949,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -10305,9 +10242,6 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -10601,9 +10535,6 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
@@ -10897,9 +10828,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -11193,9 +11121,6 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -11489,9 +11414,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -11785,9 +11707,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -12181,9 +12100,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -12477,9 +12393,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -12773,9 +12686,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -13069,9 +12979,6 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -13365,9 +13272,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -13661,9 +13565,6 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -13957,9 +13858,6 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -14253,9 +14151,6 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
@@ -14549,9 +14444,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -14845,9 +14737,6 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
@@ -15141,9 +15030,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -15437,9 +15323,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -15733,9 +15616,6 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
@@ -16129,9 +16009,6 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
@@ -16425,9 +16302,6 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -16721,9 +16595,6 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
@@ -17017,9 +16888,6 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0</v>
       </c>
@@ -17313,9 +17181,6 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -17609,9 +17474,6 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
@@ -17905,9 +17767,6 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
@@ -18201,9 +18060,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -18497,9 +18353,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -18793,9 +18646,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -19089,9 +18939,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -19385,9 +19232,6 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -19681,9 +19525,6 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -20077,9 +19918,6 @@
       <c r="O121" t="n">
         <v>0</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0</v>
       </c>
@@ -20373,9 +20211,6 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
@@ -20669,9 +20504,6 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -20965,9 +20797,6 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0</v>
       </c>
@@ -21261,9 +21090,6 @@
       <c r="O129" t="n">
         <v>0</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0</v>
       </c>
@@ -21557,9 +21383,6 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
@@ -21853,9 +21676,6 @@
       <c r="O133" t="n">
         <v>0</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0</v>
       </c>
@@ -22149,9 +21969,6 @@
       <c r="O135" t="n">
         <v>0</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0</v>
       </c>
@@ -22445,9 +22262,6 @@
       <c r="O137" t="n">
         <v>0</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0</v>
       </c>
@@ -22741,9 +22555,6 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0</v>
       </c>
@@ -23037,9 +22848,6 @@
       <c r="O141" t="n">
         <v>0</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0</v>
       </c>
@@ -23331,9 +23139,6 @@
         <v>0</v>
       </c>
       <c r="O143" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q143" t="n">
         <v>0</v>
       </c>
       <c r="R143" t="n">
